--- a/static/data/exports/Retro_NL_AE_2023.xlsx
+++ b/static/data/exports/Retro_NL_AE_2023.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -947,26 +947,26 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1950065</v>
+        <v>2001089</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lun Tungnung</t>
+          <t>AZHETO ZHIMOMI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LJPRV</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>26927</v>
+        <v>52519</v>
       </c>
       <c r="E10" t="n">
-        <v>2445</v>
+        <v>12859</v>
       </c>
       <c r="F10" t="n">
-        <v>7.67</v>
+        <v>40.34</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -982,8 +982,15 @@
           <t>NL</t>
         </is>
       </c>
-      <c r="Q10" t="b">
-        <v>0</v>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>AZHETO ZHIMOMI</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>LJPRV</t>
+        </is>
       </c>
       <c r="R10" t="n">
         <v>48</v>
@@ -999,26 +1006,26 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2001089</v>
+        <v>1950065</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AZHETO ZHIMOMI</t>
+          <t>Lun Tungnung</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LJPRV</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>52519</v>
+        <v>26927</v>
       </c>
       <c r="E11" t="n">
-        <v>12859</v>
+        <v>2445</v>
       </c>
       <c r="F11" t="n">
-        <v>40.34</v>
+        <v>7.67</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -1034,15 +1041,8 @@
           <t>NL</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>AZHETO ZHIMOMI</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>LJPRV</t>
-        </is>
+      <c r="Q11" t="b">
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>48</v>
@@ -3041,26 +3041,26 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1950105</v>
+        <v>2001091</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>R. Khing</t>
+          <t>LOGUSENG SEMP</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>RPPRINAT</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>26926</v>
+        <v>52520</v>
       </c>
       <c r="E50" t="n">
-        <v>4781</v>
+        <v>5533</v>
       </c>
       <c r="F50" t="n">
-        <v>21.2</v>
+        <v>24.54</v>
       </c>
       <c r="G50" t="n">
         <v>2</v>
@@ -3076,8 +3076,15 @@
           <t>NL</t>
         </is>
       </c>
-      <c r="Q50" t="b">
-        <v>1</v>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>LOGUSENG SEMP</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>RPPRINAT</t>
+        </is>
       </c>
       <c r="R50" t="n">
         <v>48</v>
@@ -3093,26 +3100,26 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2001091</v>
+        <v>1950105</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LOGUSENG SEMP</t>
+          <t>R. Khing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>RPPRINAT</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>52520</v>
+        <v>26926</v>
       </c>
       <c r="E51" t="n">
-        <v>5533</v>
+        <v>4781</v>
       </c>
       <c r="F51" t="n">
-        <v>24.54</v>
+        <v>21.2</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
@@ -3128,15 +3135,8 @@
           <t>NL</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>LOGUSENG SEMP</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>RPPRINAT</t>
-        </is>
+      <c r="Q51" t="b">
+        <v>1</v>
       </c>
       <c r="R51" t="n">
         <v>48</v>
@@ -4355,26 +4355,26 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1950130</v>
+        <v>2001093</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sovenyi</t>
+          <t>DR. CHOTISUH SAZO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NPF</t>
+          <t>LJPRV</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>26931</v>
+        <v>52519</v>
       </c>
       <c r="E75" t="n">
-        <v>3433</v>
+        <v>7247</v>
       </c>
       <c r="F75" t="n">
-        <v>14.89</v>
+        <v>31.44</v>
       </c>
       <c r="G75" t="n">
         <v>2</v>
@@ -4390,8 +4390,15 @@
           <t>NL</t>
         </is>
       </c>
-      <c r="Q75" t="b">
-        <v>0</v>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>DR. CHOTISUH SAZO</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>LJPRV</t>
+        </is>
       </c>
       <c r="R75" t="n">
         <v>48</v>
@@ -4407,26 +4414,26 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2001093</v>
+        <v>1950130</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DR. CHOTISUH SAZO</t>
+          <t>Sovenyi</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LJPRV</t>
+          <t>NPF</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>52519</v>
+        <v>26931</v>
       </c>
       <c r="E76" t="n">
-        <v>7247</v>
+        <v>3433</v>
       </c>
       <c r="F76" t="n">
-        <v>31.44</v>
+        <v>14.89</v>
       </c>
       <c r="G76" t="n">
         <v>2</v>
@@ -4442,15 +4449,8 @@
           <t>NL</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>DR. CHOTISUH SAZO</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>LJPRV</t>
-        </is>
+      <c r="Q76" t="b">
+        <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>48</v>
@@ -6650,26 +6650,26 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2001094</v>
+        <v>1950174</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LONGRINEKEN</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LJPRV</t>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>52519</v>
+        <v>26928</v>
       </c>
       <c r="E119" t="n">
-        <v>777</v>
+        <v>10</v>
       </c>
       <c r="F119" t="n">
-        <v>6.9</v>
+        <v>0.09</v>
       </c>
       <c r="G119" t="n">
         <v>3</v>
@@ -6685,15 +6685,8 @@
           <t>NL</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>LONGRINEKEN</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>LJPRV</t>
-        </is>
+      <c r="Q119" t="b">
+        <v>1</v>
       </c>
       <c r="R119" t="n">
         <v>48</v>
@@ -6709,26 +6702,26 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1950174</v>
+        <v>2001094</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>LONGRINEKEN</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NOTA</t>
+          <t>LJPRV</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>26928</v>
+        <v>52519</v>
       </c>
       <c r="E120" t="n">
-        <v>10</v>
+        <v>777</v>
       </c>
       <c r="F120" t="n">
-        <v>0.09</v>
+        <v>6.9</v>
       </c>
       <c r="G120" t="n">
         <v>3</v>
@@ -6744,8 +6737,15 @@
           <t>NL</t>
         </is>
       </c>
-      <c r="Q120" t="b">
-        <v>1</v>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>LONGRINEKEN</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>LJPRV</t>
+        </is>
       </c>
       <c r="R120" t="n">
         <v>48</v>
@@ -11441,26 +11441,26 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1950266</v>
+        <v>2001095</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>SETHRICHEM SANGTAM</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>NOTA</t>
+          <t>RPPRINAT</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>26928</v>
+        <v>52520</v>
       </c>
       <c r="E211" t="n">
-        <v>38</v>
+        <v>1450</v>
       </c>
       <c r="F211" t="n">
-        <v>0.19</v>
+        <v>7.16</v>
       </c>
       <c r="G211" t="n">
         <v>3</v>
@@ -11476,8 +11476,15 @@
           <t>NL</t>
         </is>
       </c>
-      <c r="Q211" t="b">
-        <v>1</v>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>SETHRICHEM SANGTAM</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>RPPRINAT</t>
+        </is>
       </c>
       <c r="R211" t="n">
         <v>48</v>
@@ -11493,26 +11500,26 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>2001095</v>
+        <v>1950266</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SETHRICHEM SANGTAM</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>RPPRINAT</t>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>52520</v>
+        <v>26928</v>
       </c>
       <c r="E212" t="n">
-        <v>1450</v>
+        <v>38</v>
       </c>
       <c r="F212" t="n">
-        <v>7.16</v>
+        <v>0.19</v>
       </c>
       <c r="G212" t="n">
         <v>3</v>
@@ -11528,15 +11535,8 @@
           <t>NL</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>SETHRICHEM SANGTAM</t>
-        </is>
-      </c>
-      <c r="L212" t="inlineStr">
-        <is>
-          <t>RPPRINAT</t>
-        </is>
+      <c r="Q212" t="b">
+        <v>1</v>
       </c>
       <c r="R212" t="n">
         <v>48</v>
